--- a/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,16 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,7 +408,10 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +718,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -735,7 +746,6 @@
           <t>NG_SB_RLOS_EXCEPTION AS A</t>
         </is>
       </c>
-      <c r="F1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -753,7 +763,6 @@
           <t>DIM_RLOS_APPLICATION AS B</t>
         </is>
       </c>
-      <c r="F2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -771,7 +780,6 @@
           <t>DIM_RLOS_EXCEPTION AS C</t>
         </is>
       </c>
-      <c r="F3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -789,7 +797,6 @@
           <t>NG_SB_RLOS_ENTRY_EXIT AS D</t>
         </is>
       </c>
-      <c r="F4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
@@ -798,7 +805,6 @@
           <t>DIM_LOS_USER AS E</t>
         </is>
       </c>
-      <c r="F5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
@@ -807,47 +813,38 @@
           <t>NG_SB_RLOS_APPLICANT_GENERAL AS F</t>
         </is>
       </c>
-      <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
       <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="n"/>
-      <c r="F9" s="52" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
       <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -875,9 +872,8 @@
           <t>How to mapping RLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -891,9 +887,8 @@
           <t>ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.EXCEPTION_CATEGORY, A.RAISED_BY, A.RAISED_DATE_TIME, A.EXCEPTION_NAME, A.EXCEPTION_REMARKS ORDER BY A.RECID DESC) = 1 AND A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -909,19 +904,18 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK (1/2) — Driving: NG_SB_RLOS_EXCEPTION. Ngày dữ liệu. Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_BK</t>
@@ -937,17 +931,16 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(A.WI_NAME || A.EXCEPTION_CATEGORY || A.RAISED_BY || TO_CHAR(A.RAISED_DATE_TIME, 'YYYY-MM-DD HH24:MI:SS'), 'MD5')</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
@@ -965,19 +958,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_SK</t>
@@ -993,19 +985,18 @@
           <t>Khóa tới ngoại lệ</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột): (1) JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM cùng category+name khác ACTIVITYNAME/DECISION_CODE; (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ. [CẦN REVIEW] Mặc định -1 nếu không còn dòng nào khớp</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột): (1) JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM cùng category+name khác ACTIVITYNAME/DECISION_CODE; (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ.</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>C.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
           <t>USER_SK</t>
@@ -1021,17 +1012,16 @@
           <t>Khóa tới người nêu lý do</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>E.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
@@ -1049,17 +1039,16 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng RLOS</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
@@ -1077,17 +1066,16 @@
           <t>Phân nhóm nội dung</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Phân nhóm nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -1105,17 +1093,16 @@
           <t>Người nêu nội dung</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Người nêu nội dung cần làm rõ. Cột USER_SK bên cạnh giữ khóa tới DIM</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_BY</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
@@ -1133,17 +1120,16 @@
           <t>Thời điểm nêu nội dung</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Thời điểm nêu nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
@@ -1161,17 +1147,16 @@
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
@@ -1189,19 +1174,18 @@
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
           <t>RCTYPE</t>
@@ -1217,19 +1201,18 @@
           <t>Loại ghi nhận</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT</t>
@@ -1245,200 +1228,72 @@
           <t>Sản phẩm vay chi tiết</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>F.SUB_PRODUCT</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="85" customHeight="1"/>
+    </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="10" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="D31" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
       <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+    </row>
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="25" t="n"/>
       <c r="B32" s="25" t="n"/>
       <c r="C32" s="51" t="n"/>
-      <c r="D32" s="8" t="n"/>
+      <c r="D32" s="54" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="25" t="n"/>
       <c r="B33" s="25" t="n"/>
       <c r="C33" s="51" t="n"/>
-      <c r="D33" s="8" t="n"/>
+      <c r="D33" s="54" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="25" t="n"/>
       <c r="C34" s="51" t="n"/>
-      <c r="D34" s="8" t="n"/>
+      <c r="D34" s="54" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
       <c r="C35" s="51" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="54" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1"/>
-    <row r="37" ht="51" customHeight="1"/>
-    <row r="38" ht="51" customHeight="1"/>
-    <row r="39" ht="34" customHeight="1"/>
-    <row r="40" ht="34" customHeight="1"/>
-    <row r="41" ht="34" customHeight="1"/>
-    <row r="42" ht="17" customHeight="1"/>
-    <row r="43" ht="34" customHeight="1"/>
-    <row r="44" ht="17" customHeight="1"/>
-    <row r="45" ht="85" customHeight="1"/>
-    <row r="46" ht="34" customHeight="1"/>
-    <row r="47" ht="17" customHeight="1"/>
-    <row r="48" ht="17" customHeight="1"/>
-    <row r="49" ht="17" customHeight="1"/>
-    <row r="50" ht="51" customHeight="1"/>
-    <row r="51" ht="51" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -409,6 +409,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,7 +758,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng Fact ngoại lệ/nội dung cần làm rõ RLOS, driving từ NG_SB_RLOS_EXCEPTION</t>
+          <t>Bảng FACT ghi nhận từng lần một lý do (nội dung cần làm rõ) được nêu ra trên hồ sơ tín dụng RLOS trong quá trình xử lý (cả Raise và Clear)</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -873,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -882,11 +885,7 @@
           <t>Điều kiện lấy dữ liệu</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.EXCEPTION_CATEGORY, A.RAISED_BY, A.RAISED_DATE_TIME, A.EXCEPTION_NAME, A.EXCEPTION_REMARKS ORDER BY A.RECID DESC) = 1 AND A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL</t>
-        </is>
-      </c>
+      <c r="E16" s="6" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
@@ -906,7 +905,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Driving: NG_SB_RLOS_EXCEPTION. Ngày dữ liệu. Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
+          <t>Ngày dữ liệu. Ảnh chụp đầy đủ theo ngày (quy trình A2). Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -915,7 +914,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_BK</t>
@@ -928,12 +927,12 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ</t>
+          <t>Khóa nghiệp vụ dòng ngoại lệ</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn</t>
+          <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn. PK đổi từ composite (DAYID,WI_NAME,EXCEPTION_CATEGORY,RAISED_BY,RAISED_DATE_TIME) thành (DAYID,EXCEPTION_BK). Không có thành phần DATASOURCE trong công thức hash.</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -942,7 +941,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -955,12 +954,12 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
@@ -970,325 +969,417 @@
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_SK</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột): (1) JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM cùng category+name khác ACTIVITYNAME/DECISION_CODE; (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ.</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>C.DIMENSION_KEY</t>
-        </is>
-      </c>
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="55" t="inlineStr">
+        <is>
+          <t>Filter sau khi hash: ROW_NUMBER() OVER (PARTITION BY WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME, EXCEPTION_NAME, EXCEPTION_REMARKS ORDER BY RECID DESC) = 1; Filter từ nguồn: A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng RLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Khóa ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — 2 bước: (1) LEFT JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM cùng category+name khác ACTIVITYNAME/DECISION_CODE; (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ (D). Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_RLOS_EXCEPTION_REASON→DIM_RLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>C.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>WORKSTEP_CODE</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã bước xử lý ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_RLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_RLOS_EXCEPTION</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>C.ACTIVITYNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>DECISION_CODE</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Mã quyết định ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_RLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>C.DECISION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>USER_SK</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới người nêu lý do</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Khóa người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1 nếu không khớp. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>E.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>WI_NAME</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>USERNAME</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(150)</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Tên tài khoản người nêu</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_CATEGORY</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Phân nhóm nội dung</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>A.EXCEPTION_CATEGORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>RAISED_BY</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng RLOS</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>RAISED_DATE_TIME</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu lý do</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_DATE_TIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_NAME</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>RAISED_BY</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Người nêu nội dung</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Người nêu nội dung cần làm rõ. Cột USER_SK bên cạnh giữ khóa tới DIM</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>A.RAISED_BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>RAISED_DATE_TIME</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm nêu nội dung</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Thời điểm nêu nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>A.RAISED_DATE_TIME</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_NAME</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(500)</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Tên nội dung ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>Tên nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>RCTYPE</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Loại ghi nhận</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
-        <is>
-          <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp.</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(255)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Sản phẩm vay chi tiết</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
-        <is>
-          <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR</t>
-        </is>
-      </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Cùng cơ chế đã áp dụng cho CLOS (CUSTOMER_SK). Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR (đã chuyển hẳn sang PDTD_DTM).</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>F.SUB_PRODUCT</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="55" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="56" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="51" t="n"/>
-      <c r="D32" s="54" t="n"/>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="51" t="n"/>
+      <c r="D36" s="54" t="n"/>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="51" t="n"/>
-      <c r="D33" s="54" t="n"/>
-      <c r="E33" s="8" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="51" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="51" t="n"/>
-      <c r="D34" s="54" t="n"/>
-      <c r="E34" s="8" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="51" t="n"/>
+      <c r="D38" s="54" t="n"/>
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="51" t="n"/>
-      <c r="D35" s="54" t="n"/>
-      <c r="E35" s="8" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="25" t="n"/>
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="51" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.WI_NAME = A.WI_NAME</t>
         </is>

--- a/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -409,9 +409,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -876,7 +873,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -885,7 +882,11 @@
           <t>Điều kiện lấy dữ liệu</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL AND ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.EXCEPTION_CATEGORY, A.RAISED_BY, A.RAISED_DATE_TIME, A.EXCEPTION_NAME, A.EXCEPTION_REMARKS ORDER BY A.RECID DESC) = 1</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
@@ -968,418 +969,407 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="55" t="inlineStr">
-        <is>
-          <t>Filter sau khi hash: ROW_NUMBER() OVER (PARTITION BY WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME, EXCEPTION_NAME, EXCEPTION_REMARKS ORDER BY RECID DESC) = 1; Filter từ nguồn: A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng RLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="150" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>WI_NAME</t>
+          <t>EXCEPTION_SK</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng</t>
+          <t>Khóa ngoại lệ</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng RLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Khóa tới DIM_RLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — 2 bước: (1) LEFT JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM cùng category+name khác ACTIVITYNAME/DECISION_CODE; (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ (D). Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_RLOS_EXCEPTION_REASON→DIM_RLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="150" customHeight="1">
+          <t>C.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_SK</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Mã bước xử lý ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_RLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_RLOS_EXCEPTION</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>C.ACTIVITYNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>DECISION_CODE</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã quyết định ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_RLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>C.DECISION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>USER_SK</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — 2 bước: (1) LEFT JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM cùng category+name khác ACTIVITYNAME/DECISION_CODE; (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ (D). Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_RLOS_EXCEPTION_REASON→DIM_RLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>C.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>WORKSTEP_CODE</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Mã bước xử lý ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_RLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_RLOS_EXCEPTION</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>C.ACTIVITYNAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>DECISION_CODE</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Mã quyết định ngoại lệ</t>
+          <t>Khóa người nêu lý do</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_RLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1 nếu không khớp. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>C.DECISION_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t>E.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>USER_SK</t>
+          <t>USERNAME</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(150)</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Khóa người nêu lý do</t>
+          <t>Tên tài khoản người nêu</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1 nếu không khớp. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
+          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>E.DIMENSION_KEY</t>
+          <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>USERNAME</t>
+          <t>EXCEPTION_CATEGORY</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(150)</t>
+          <t>VARCHAR2(500)</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Tên tài khoản người nêu</t>
+          <t>Phân nhóm nội dung</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
+          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
+          <t>A.EXCEPTION_CATEGORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>RAISED_BY</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
           <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>RAISED_DATE_TIME</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu lý do</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_DATE_TIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_NAME</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung</t>
-        </is>
-      </c>
-      <c r="D27" s="54" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>RAISED_BY</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Người nêu lý do</t>
-        </is>
-      </c>
-      <c r="D28" s="54" t="inlineStr">
-        <is>
-          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>A.RAISED_BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>RAISED_DATE_TIME</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm nêu lý do</t>
+          <t>Tên nội dung ngoại lệ</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_DATE_TIME</t>
+          <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_NAME</t>
+          <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>VARCHAR2(4000)</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Tên nội dung ngoại lệ</t>
+          <t>Ghi chú ngoại lệ</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Tên nội dung cần làm rõ</t>
+          <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+          <t>A.EXCEPTION_REMARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_REMARKS</t>
+          <t>RCTYPE</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(4000)</t>
+          <t>VARCHAR2(20)</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Ghi chú ngoại lệ</t>
+          <t>Loại ghi nhận</t>
         </is>
       </c>
       <c r="D31" s="54" t="inlineStr">
         <is>
-          <t>Ghi chú của nội dung cần làm rõ</t>
+          <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp.</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_REMARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+          <t>A.RCTYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>RCTYPE</t>
+          <t>SUB_PRODUCT</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(20)</t>
+          <t>VARCHAR2(255)</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Loại ghi nhận</t>
+          <t>Sản phẩm vay chi tiết</t>
         </is>
       </c>
       <c r="D32" s="54" t="inlineStr">
         <is>
-          <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp.</t>
+          <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Cùng cơ chế đã áp dụng cho CLOS (CUSTOMER_SK). Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR (đã chuyển hẳn sang PDTD_DTM).</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>A.RCTYPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>SUB_PRODUCT</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(255)</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Sản phẩm vay chi tiết</t>
-        </is>
-      </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Cùng cơ chế đã áp dụng cho CLOS (CUSTOMER_SK). Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR (đã chuyển hẳn sang PDTD_DTM).</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
           <t>F.SUB_PRODUCT</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="56" t="inlineStr">
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E35" s="10" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="51" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="25" t="n"/>
       <c r="B36" s="25" t="n"/>
       <c r="C36" s="51" t="n"/>
       <c r="D36" s="54" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
+          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="25" t="n"/>
       <c r="B37" s="25" t="n"/>
       <c r="C37" s="51" t="n"/>
       <c r="D37" s="54" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
+          <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="25" t="n"/>
       <c r="C38" s="51" t="n"/>
       <c r="D38" s="54" t="n"/>
       <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="25" t="n"/>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="51" t="n"/>
-      <c r="D39" s="54" t="n"/>
-      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.WI_NAME = A.WI_NAME</t>
         </is>

--- a/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -413,6 +413,9 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -718,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -777,7 +780,7 @@
       </c>
       <c r="E3" s="52" t="inlineStr">
         <is>
-          <t>DIM_RLOS_EXCEPTION AS C</t>
+          <t>DIM_LOS_USER AS C</t>
         </is>
       </c>
     </row>
@@ -794,25 +797,17 @@
       </c>
       <c r="E4" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_RLOS_ENTRY_EXIT AS D</t>
+          <t>NG_SB_RLOS_APPLICANT_GENERAL AS D</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
-      <c r="E5" s="52" t="inlineStr">
-        <is>
-          <t>DIM_LOS_USER AS E</t>
-        </is>
-      </c>
+      <c r="E5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
-      <c r="E6" s="52" t="inlineStr">
-        <is>
-          <t>NG_SB_RLOS_APPLICANT_GENERAL AS F</t>
-        </is>
-      </c>
+      <c r="E6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
@@ -996,10 +991,10 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="150" customHeight="1">
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_SK</t>
+          <t>USER_SK</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
@@ -1009,12 +1004,12 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa ngoại lệ</t>
+          <t>Khóa người nêu lý do</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_EXCEPTION — PHÁI SINH 2 bước đúng SRS BC7 (không phải lookup 1 cột). Không phải lookup 1 cột đơn giản — 2 bước: (1) LEFT JOIN theo EXCEPTION_CATEGORY+EXCEPTION_NAME có thể khớp nhiều dòng DIM cùng category+name khác ACTIVITYNAME/DECISION_CODE; (2) EXISTS lọc còn đúng tổ hợp đã thực sự xảy ra trong lịch sử xử lý hồ sơ (D). Mặc định -1 nếu không còn dòng nào khớp. Bảng đích đổi tên từ DIM_RLOS_EXCEPTION_REASON→DIM_RLOS_EXCEPTION, cột SK đổi tên EXCEPTION_REASON_SK→EXCEPTION_SK</t>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1 nếu không khớp. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
@@ -1023,118 +1018,118 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>WORKSTEP_CODE</t>
+          <t>USERNAME</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>VARCHAR2(150)</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Mã bước xử lý ngoại lệ</t>
+          <t>Tên tài khoản người nêu</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: tương ứng ACTIVITYNAME của dòng DIM_RLOS_EXCEPTION đã khớp EXCEPTION_SK, 1 phần BK composite 4 cột của DIM_RLOS_EXCEPTION</t>
+          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>C.ACTIVITYNAME</t>
+          <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>DECISION_CODE</t>
+          <t>EXCEPTION_CATEGORY</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>VARCHAR2(500)</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Mã quyết định ngoại lệ</t>
+          <t>Phân nhóm nội dung</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: phần còn lại của BK composite DIM_RLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK</t>
+          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>C.DECISION_CODE</t>
+          <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>USER_SK</t>
+          <t>RAISED_BY</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Khóa người nêu lý do</t>
+          <t>Người nêu lý do</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1 nếu không khớp. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
+          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>E.DIMENSION_KEY</t>
+          <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>USERNAME</t>
+          <t>RAISED_DATE_TIME</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(150)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Tên tài khoản người nêu</t>
+          <t>Thời điểm nêu lý do</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
+          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+          <t>A.RAISED_DATE_TIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_CATEGORY</t>
+          <t>EXCEPTION_NAME</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
@@ -1144,234 +1139,154 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung</t>
+          <t>Tên nội dung ngoại lệ</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t>A.EXCEPTION_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>RAISED_BY</t>
+          <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(4000)</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Người nêu lý do</t>
+          <t>Ghi chú ngoại lệ</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_BY</t>
+          <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>RAISED_DATE_TIME</t>
+          <t>RCTYPE</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR2(20)</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm nêu lý do</t>
+          <t>Loại ghi nhận</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+          <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp.</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_DATE_TIME</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+          <t>A.RCTYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_NAME</t>
+          <t>SUB_PRODUCT</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>VARCHAR2(255)</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Tên nội dung ngoại lệ</t>
+          <t>Sản phẩm vay chi tiết</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Tên nội dung cần làm rõ</t>
+          <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Cùng cơ chế đã áp dụng cho CLOS (CUSTOMER_SK). Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR (đã chuyển hẳn sang PDTD_DTM).</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_REMARKS</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(4000)</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Ghi chú của nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_REMARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>RCTYPE</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(20)</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Loại ghi nhận</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp.</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>A.RCTYPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>SUB_PRODUCT</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(255)</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Sản phẩm vay chi tiết</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Cùng cơ chế đã áp dụng cho CLOS (CUSTOMER_SK). Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR (đã chuyển hẳn sang PDTD_DTM).</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
-        <is>
-          <t>F.SUB_PRODUCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="55" t="inlineStr">
+          <t>D.SUB_PRODUCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E34" s="10" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="51" t="n"/>
-      <c r="D35" s="54" t="n"/>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="25" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="51" t="n"/>
+      <c r="D32" s="54" t="n"/>
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="51" t="n"/>
-      <c r="D36" s="54" t="n"/>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.EXCEPTION_NAME = A.EXCEPTION_NAME AND EXISTS (SELECT 1 FROM D WHERE D.WINAME = A.WI_NAME AND D.WORKSTEP = C.ACTIVITYNAME AND D.DECISION = C.DECISION_CODE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="25" t="n"/>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="51" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN E.EFF_DATE AND NVL(E.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="25" t="n"/>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="51" t="n"/>
-      <c r="D38" s="54" t="n"/>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F.WI_NAME = A.WI_NAME</t>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="51" t="n"/>
+      <c r="D33" s="54" t="n"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN C.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="51" t="n"/>
+      <c r="D34" s="54" t="n"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN D.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>Chú ý:</t>
+        </is>
+      </c>
+      <c r="B37" s="56" t="inlineStr">
+        <is>
+          <t>1. SRS BC7 cập nhật 2026-10-28: bỏ EXCEPTION_SK/WORKSTEP_CODE/DECISION_CODE — FCT không còn lookup sang DIM_RLOS_EXCEPTION ở tầng SB_DWH (thuật toán mới không còn đủ khóa EXCEPTION_NAME để lookup DIM 1:1 ổn định). Việc tính WORKSTEP_CODE (thay ACTIVITYNAME) chuyển hẳn xuống PDTD_DTM.</t>
         </is>
       </c>
     </row>

--- a/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_EXCEPTION.xlsx
@@ -411,11 +411,11 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng FACT ghi nhận từng lần một lý do (nội dung cần làm rõ) được nêu ra trên hồ sơ tín dụng RLOS trong quá trình xử lý (cả Raise và Clear)</t>
+          <t>Ghi nhận các ngoại lệ/nội dung cần làm rõ (exception) phát sinh trong quá trình xử lý hồ sơ RLOS</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -868,7 +868,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -877,11 +877,7 @@
           <t>Điều kiện lấy dữ liệu</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL AND ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.EXCEPTION_CATEGORY, A.RAISED_BY, A.RAISED_DATE_TIME, A.EXCEPTION_NAME, A.EXCEPTION_REMARKS ORDER BY A.RECID DESC) = 1</t>
-        </is>
-      </c>
+      <c r="E16" s="6" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
@@ -901,7 +897,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>Ngày dữ liệu. Ảnh chụp đầy đủ theo ngày (quy trình A2). Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME.</t>
+          <t>PK (1/2) — Driving: NG_SB_RLOS_EXCEPTION. Ngày dữ liệu. Ảnh chụp đầy đủ theo ngày (quy trình A2). Nguồn LOẠI 1, khóa CDC khai đủ WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -910,7 +906,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="90" customHeight="1">
+    <row r="18" ht="105" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_BK</t>
@@ -923,17 +919,17 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ dòng ngoại lệ</t>
+          <t>Khóa nghiệp vụ ngoại lệ</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn. PK đổi từ composite (DAYID,WI_NAME,EXCEPTION_CATEGORY,RAISED_BY,RAISED_DATE_TIME) thành (DAYID,EXCEPTION_BK). Không có thành phần DATASOURCE trong công thức hash.</t>
+          <t>Khóa nghiệp vụ của dòng ngoại lệ — gộp 4 cột PK tự nhiên cũ (WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME) thành 1 khóa đơn. PK đổi từ composite (DAYID,WI_NAME,EXCEPTION_CATEGORY,RAISED_BY,RAISED_DATE_TIME) thành (DAYID,EXCEPTION_BK). Không có thành phần DATASOURCE trong công thức hash (cột DATASOURCE không có trong thiết kế bảng).</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>STANDARD_HASH(A.WI_NAME || A.EXCEPTION_CATEGORY || A.RAISED_BY || TO_CHAR(A.RAISED_DATE_TIME, 'YYYY-MM-DD HH24:MI:SS'), 'MD5')</t>
+          <t>STANDARD_HASH(A.WI_NAME || A.EXCEPTION_CATEGORY || A.RAISED_BY || TO_CHAR(A.RAISED_DATE_TIME, 'YYYY-MM-DD HH24:MI:SS')||A.RECID, 'MD5')</t>
         </is>
       </c>
     </row>
@@ -950,7 +946,7 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa hồ sơ tín dụng</t>
+          <t>Khóa tới DIM_RLOS_APPLICATION</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
@@ -964,329 +960,355 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="55" t="inlineStr">
+        <is>
+          <t>Filter sau khi hash ROW_NUMBER() OVER (PARTITION BY WI_NAME, EXCEPTION_CATEGORY, RAISED_BY, RAISED_DATE_TIME, EXCEPTION_NAME, EXCEPTION_REMARKS ORDER BY RECID DESC) = 1. Filter từ nguồn: AND A.RAISED_BY IS NOT NULL AND A.RAISED_DATE_TIME IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>WI_NAME</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng RLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng RLOS</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>PK (2/5) — mã hồ sơ tín dụng RLOS. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>USER_SK</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Khóa người nêu lý do</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_LOS_USER, người nêu lý do. Mặc định -1 nếu không khớp. ĐÚNG GRAIN của bảng — 1 lần ghi nhận lý do có đúng 1 người nêu. Đổi tên từ RAISED_BY_USER_SK→USER_SK theo HLD</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>C.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
+    <row r="23" ht="75" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(150)</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Tên tài khoản người nêu</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Tên tài khoản (BK của DIM_LOS_USER)</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: Tên tài khoản dùng để lookup USER_SK, giữ tách biệt khỏi cột RAISED_BY (hiển thị) dù cùng nguồn giá trị. Không JOIN thêm — lấy từ cùng A.RAISED_BY đã dùng để tra USER_SK. Giữ tách biệt ý nghĩa khóa nghiệp vụ (USERNAME, BK của DIM_LOS_USER) khỏi cột nghiệp vụ hiển thị (RAISED_BY).</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(500)</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>EXCEPTION_CATEGORY</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Phân nhóm nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>PK (3/5) — phân nhóm nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>A.EXCEPTION_CATEGORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>RAISED_BY</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Người nêu lý do</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Người nêu nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>PK (4/5) — người nêu nội dung cần làm rõ. Cột USERNAME bên cạnh giữ khóa tới DIM. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm nêu lý do</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>PK (5/5) — thời điểm nêu nội dung cần làm rõ. Không còn là thành phần PK riêng lẻ — PK đã gộp vào EXCEPTION_BK (DAYID+EXCEPTION_BK).</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_DATE_TIME</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>EXCEPTION_NAME</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(500)</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>Tên nội dung ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>Tên nội dung cần làm rõ</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
+          <t>EXCEPTION_NAME</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Tên nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>Tên nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>A.EXCEPTION_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
           <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú ngoại lệ</t>
-        </is>
-      </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>RCTYPE</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Loại ghi nhận</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Loại ghi nhận, Raise hay Clear. SRS BC7 không còn dùng cột này làm điều kiện lọc CHECK_FTR — vẫn giữ cột vì BC7 hiển thị trực tiếp.</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(255)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Sản phẩm vay chi tiết</t>
-        </is>
-      </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Sản phẩm vay chi tiết (thô)</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>Sản phẩm vay chi tiết tự khai theo hồ sơ — cột thô. Cùng cơ chế đã áp dụng cho CLOS (CUSTOMER_SK). Không tính BI_SUB_PRODUCT ở đây — chỉ giữ giá trị gốc, PDTD_DTM tự CASE WHEN phân loại 'Credit Card' khi tính CHECK_FTR (đã chuyển hẳn sang PDTD_DTM).</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>D.SUB_PRODUCT</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="55" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>TIME_UPDATE</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm cập nhật bản ghi</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm bản ghi được cập nhật lần gần nhất (audit column). Audit column — thời điểm bản ghi được ETL job cập nhật lần gần nhất</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP()</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="56" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="51" t="n"/>
-      <c r="D32" s="54" t="n"/>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="51" t="n"/>
-      <c r="D33" s="54" t="n"/>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="25" t="n"/>
       <c r="B34" s="25" t="n"/>
       <c r="C34" s="51" t="n"/>
       <c r="D34" s="54" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="51" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN C.USERNAME = A.RAISED_BY AND v_batch_date BETWEEN C.EFF_DATE AND NVL(C.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="51" t="n"/>
+      <c r="D36" s="54" t="n"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
           <t>LEFT JOIN D.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="56" t="inlineStr">
-        <is>
-          <t>Chú ý:</t>
-        </is>
-      </c>
-      <c r="B37" s="56" t="inlineStr">
-        <is>
-          <t>1. SRS BC7 cập nhật 2026-10-28: bỏ EXCEPTION_SK/WORKSTEP_CODE/DECISION_CODE — FCT không còn lookup sang DIM_RLOS_EXCEPTION ở tầng SB_DWH (thuật toán mới không còn đủ khóa EXCEPTION_NAME để lookup DIM 1:1 ổn định). Việc tính WORKSTEP_CODE (thay ACTIVITYNAME) chuyển hẳn xuống PDTD_DTM.</t>
         </is>
       </c>
     </row>
